--- a/results/Int Task Remove ACC -1.0/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_4_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.71740401170618</v>
+        <v>0.7113502383684196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.71740401170618</v>
+        <v>0.7111812510594542</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7189795337981623</v>
+        <v>0.7114607368056811</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7159389880514591</v>
+        <v>0.7102751988971872</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7090103332674895</v>
+        <v>0.7136719313655856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7096031022217366</v>
+        <v>0.7009598829382007</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7096031022217366</v>
+        <v>0.6996391551825343</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7043331498113646</v>
+        <v>0.7009378182740249</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.708304439130246</v>
+        <v>0.7005205159348904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.703537596086359</v>
+        <v>0.705434281623567</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7130036872505467</v>
+        <v>0.7035883798372398</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7107769073326133</v>
+        <v>0.7031490128339295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7062375404693959</v>
+        <v>0.6945642824220977</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.707143592631663</v>
+        <v>0.6945642824220977</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.660559307715908</v>
+        <v>0.6907710864640639</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6854867745103396</v>
+        <v>0.6834979777560166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6829129139225929</v>
+        <v>0.6873769807414007</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6829129139225929</v>
+        <v>0.6765719497177825</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.686503325109868</v>
+        <v>0.6913391640083999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6827348205617454</v>
+        <v>0.6875056912824263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6827348205617454</v>
+        <v>0.6783710954300228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6827348205617454</v>
+        <v>0.6755177490960492</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6794576925824903</v>
+        <v>0.6791757552069105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6787206277291888</v>
+        <v>0.6744765070866098</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6603707073721194</v>
+        <v>0.6764393866163452</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6603707073721194</v>
+        <v>0.6806901616814536</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.653343286948506</v>
+        <v>0.6821122818224992</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.647589838206472</v>
+        <v>0.6621050600228913</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6314666977673362</v>
+        <v>0.6604801551110868</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6349219191074388</v>
+        <v>0.6537660178954934</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6346307005635945</v>
+        <v>0.6453138505850988</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6392182244319575</v>
+        <v>0.647215614497395</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6324676630088357</v>
+        <v>0.6336612562709176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6326613417277123</v>
+        <v>0.6329670949312913</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6337454872508269</v>
+        <v>0.6329670949312913</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6443906370173618</v>
+        <v>0.6383331862355721</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6732217982070884</v>
+        <v>0.6533005585512132</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6735259753632264</v>
+        <v>0.6687787453541624</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.67326592753544</v>
+        <v>0.6475574416757377</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6675292899661115</v>
+        <v>0.6457362312993216</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6475831837839428</v>
+        <v>0.6650804624753612</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.65149598423112</v>
+        <v>0.6650804624753612</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6692062044434732</v>
+        <v>0.6609557712055432</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6786202860421036</v>
+        <v>0.6614900512880861</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.651646584319939</v>
+        <v>0.6637688407715768</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6489440131911669</v>
+        <v>0.6643616097258238</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6454978979029463</v>
+        <v>0.6509345611093132</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6496784512987331</v>
+        <v>0.6794550658367551</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6476115526378832</v>
+        <v>0.6794550658367551</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6518714337548734</v>
+        <v>0.687794107964153</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6359472255260846</v>
+        <v>0.6885467581754834</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6340090374062602</v>
+        <v>0.6850083565537657</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6336840214006229</v>
+        <v>0.6304461194910138</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6334045356543959</v>
+        <v>0.5935983054337912</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6266851449473321</v>
+        <v>0.5182529058812486</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6007644180322242</v>
+        <v>0.5419310924040117</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5999259607935434</v>
+        <v>0.5314120264327672</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5485032102335212</v>
+        <v>0.5561172705379995</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.549909745016538</v>
+        <v>0.5568114318776258</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5536353460509854</v>
+        <v>0.5524566376814031</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5123546358910132</v>
+        <v>0.5628457672969456</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5240904104868095</v>
+        <v>0.5755669217762125</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5265966761509699</v>
+        <v>0.5817585117068804</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5284425779372971</v>
+        <v>0.5644720731398087</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5034734334438667</v>
+        <v>0.556430728862402</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5046927688141539</v>
+        <v>0.5678609253710016</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5048552768169725</v>
+        <v>0.5439016770545705</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5010932515749967</v>
+        <v>0.5508665809296859</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5005004826207498</v>
+        <v>0.5503414068990251</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5007708623150946</v>
+        <v>0.5341597775881851</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5007708623150946</v>
+        <v>0.5299181085749589</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5014923418103672</v>
+        <v>0.5354519613735289</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5021006961226431</v>
+        <v>0.528826257931021</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.501787412914623</v>
+        <v>0.5311635362862158</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.501787412914623</v>
+        <v>0.4997117584346557</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.501787412914623</v>
+        <v>0.4690581610538364</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5019564002235886</v>
+        <v>0.4675201138676764</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5032186391075508</v>
+        <v>0.4741146465941264</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5032186391075508</v>
+        <v>0.4874818054078741</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5030743432084964</v>
+        <v>0.4874818054078741</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5008384572386808</v>
+        <v>0.5006917097102734</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5005251740306608</v>
+        <v>0.5054259811070437</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5008046597768877</v>
+        <v>0.5018264638678865</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5005589714924539</v>
+        <v>0.5026649211065675</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5002794857462269</v>
+        <v>0.5010309101428809</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>0.5008775081919443</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.49820610777923</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4995606329966896</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5002794857462269</v>
+        <v>0.4995606329966896</v>
       </c>
     </row>
   </sheetData>
